--- a/staff_forms/005_new_user_request_form--staff_forms.xlsx
+++ b/staff_forms/005_new_user_request_form--staff_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,8 +431,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,7 +515,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>first_name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,7 +538,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>last_name</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,7 +561,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,7 +584,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,7 +607,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>department</t>
+          <t>Department</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,7 +630,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>job_title</t>
+          <t>Job Title</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,7 +653,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>request_reason</t>
+          <t>Reason for Requesting Account</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,7 +676,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>Submit</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,7 +699,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>Assigned Tool</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,7 +722,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>Form ID</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -740,12 +740,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>first_name</t>
+          <t>repeat_first_name</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>first_name</t>
+          <t>Repeat First Name</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -763,12 +763,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>last_name</t>
+          <t>repeat_last_name</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>last_name</t>
+          <t>Repeat Last Name</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -786,12 +786,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>repeat_email</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Repeat Email</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -809,12 +809,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>repeat_phone</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>Repeat Phone</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -832,12 +832,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>department</t>
+          <t>repeat_department</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>department</t>
+          <t>Repeat Department</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -855,12 +855,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>job_title</t>
+          <t>repeat_job_title</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>job_title</t>
+          <t>Repeat Job Title</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -878,12 +878,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>request_reason</t>
+          <t>repeat_request_reason</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>request_reason</t>
+          <t>Repeat Request Reason</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -901,12 +901,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>repeat_submit</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>Repeat Submit</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -924,12 +924,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>repeat_assigned_tool</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>Repeat Assigned Tool</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -947,12 +947,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>repeat_form_id</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>Repeat Form Id</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -970,12 +970,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>department</t>
+          <t>repeat_department_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>department</t>
+          <t>Repeat Department 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -993,12 +993,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>job_title</t>
+          <t>repeat_job_title_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>job_title</t>
+          <t>Repeat Job Title 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1016,12 +1016,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>request_reason</t>
+          <t>repeat_request_reason_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>request_reason</t>
+          <t>Repeat Request Reason 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1039,12 +1039,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>repeat_assigned_tool_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>Repeat Assigned Tool 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1062,12 +1062,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>repeat_form_id_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>Repeat Form Id 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
